--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:N418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20370,6 +20370,150 @@
         <v>336.58</v>
       </c>
       <c r="N415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="C416" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="D416" t="n">
+        <v>326.87</v>
+      </c>
+      <c r="E416" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="F416" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="G416" t="n">
+        <v>333.17</v>
+      </c>
+      <c r="H416" t="n">
+        <v>337.39</v>
+      </c>
+      <c r="I416" t="n">
+        <v>340.17</v>
+      </c>
+      <c r="J416" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="K416" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="L416" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="M416" t="n">
+        <v>341.22</v>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="C417" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="D417" t="n">
+        <v>326.94</v>
+      </c>
+      <c r="E417" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="F417" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="G417" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="H417" t="n">
+        <v>336.45</v>
+      </c>
+      <c r="I417" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="J417" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="K417" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="L417" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="M417" t="n">
+        <v>341.22</v>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>334.24</v>
+      </c>
+      <c r="C418" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D418" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="E418" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="F418" t="n">
+        <v>327.51</v>
+      </c>
+      <c r="G418" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="H418" t="n">
+        <v>335.98</v>
+      </c>
+      <c r="I418" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="J418" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="K418" t="n">
+        <v>341.43</v>
+      </c>
+      <c r="L418" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="M418" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="N418" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20386,7 +20530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24799,6 +24943,36 @@
       </c>
       <c r="B441" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -24967,28 +25141,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1902917752823896</v>
+        <v>-0.197579956306436</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09104339454818711</v>
+        <v>0.09783016782591047</v>
       </c>
       <c r="M2" t="n">
-        <v>3.666541341342997</v>
+        <v>3.679019194783713</v>
       </c>
       <c r="N2" t="n">
-        <v>22.074344842495</v>
+        <v>22.14069999612402</v>
       </c>
       <c r="O2" t="n">
-        <v>4.698334262533371</v>
+        <v>4.705390525357489</v>
       </c>
       <c r="P2" t="n">
-        <v>344.8387990719576</v>
+        <v>344.9140113167222</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25045,28 +25219,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.164636197147385</v>
+        <v>-0.1720157771998533</v>
       </c>
       <c r="J3" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06413645639566756</v>
+        <v>0.06992266892267185</v>
       </c>
       <c r="M3" t="n">
-        <v>3.632669969904242</v>
+        <v>3.638642179764911</v>
       </c>
       <c r="N3" t="n">
-        <v>24.14967551665398</v>
+        <v>24.2062604491517</v>
       </c>
       <c r="O3" t="n">
-        <v>4.914231935577927</v>
+        <v>4.919985817982782</v>
       </c>
       <c r="P3" t="n">
-        <v>337.7710157281759</v>
+        <v>337.8471715356072</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25123,28 +25297,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08105005599503678</v>
+        <v>-0.08678211721625002</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01456685701140026</v>
+        <v>0.01681746742680745</v>
       </c>
       <c r="M4" t="n">
-        <v>3.750648372135744</v>
+        <v>3.745135255459675</v>
       </c>
       <c r="N4" t="n">
-        <v>27.13445012947741</v>
+        <v>27.07846968544984</v>
       </c>
       <c r="O4" t="n">
-        <v>5.209073826456811</v>
+        <v>5.203697693510821</v>
       </c>
       <c r="P4" t="n">
-        <v>333.674046180494</v>
+        <v>333.7331990660118</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25201,28 +25375,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08969919731507092</v>
+        <v>-0.09721413968403131</v>
       </c>
       <c r="J5" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01722780876908969</v>
+        <v>0.02029119987915562</v>
       </c>
       <c r="M5" t="n">
-        <v>4.008027765085288</v>
+        <v>4.013901653864631</v>
       </c>
       <c r="N5" t="n">
-        <v>28.02547675186297</v>
+        <v>28.06326709130397</v>
       </c>
       <c r="O5" t="n">
-        <v>5.293909401554107</v>
+        <v>5.297477427163232</v>
       </c>
       <c r="P5" t="n">
-        <v>334.9919105603744</v>
+        <v>335.0694626589004</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25279,28 +25453,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02752918275282311</v>
+        <v>0.01859988883813053</v>
       </c>
       <c r="J6" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001982820342719349</v>
+        <v>0.0009060729434116066</v>
       </c>
       <c r="M6" t="n">
-        <v>3.814125197875957</v>
+        <v>3.833872705817264</v>
       </c>
       <c r="N6" t="n">
-        <v>23.29133426506652</v>
+        <v>23.46140031130336</v>
       </c>
       <c r="O6" t="n">
-        <v>4.826109640804539</v>
+        <v>4.843696967328092</v>
       </c>
       <c r="P6" t="n">
-        <v>333.6513701861853</v>
+        <v>333.7435195337139</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25357,28 +25531,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08761739695246429</v>
+        <v>0.07934334707671638</v>
       </c>
       <c r="J7" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K7" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01816824487390933</v>
+        <v>0.01498966897117504</v>
       </c>
       <c r="M7" t="n">
-        <v>3.783026853584613</v>
+        <v>3.80003960596512</v>
       </c>
       <c r="N7" t="n">
-        <v>25.33132294065388</v>
+        <v>25.44250408263069</v>
       </c>
       <c r="O7" t="n">
-        <v>5.033023240623262</v>
+        <v>5.044056312396868</v>
       </c>
       <c r="P7" t="n">
-        <v>336.1655936309944</v>
+        <v>336.25098414442</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25435,28 +25609,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1629411230288831</v>
+        <v>0.161400481751841</v>
       </c>
       <c r="J8" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K8" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04577792839426897</v>
+        <v>0.04556306622612993</v>
       </c>
       <c r="M8" t="n">
-        <v>4.226314204408</v>
+        <v>4.201227081358475</v>
       </c>
       <c r="N8" t="n">
-        <v>33.79152656742189</v>
+        <v>33.56093275553273</v>
       </c>
       <c r="O8" t="n">
-        <v>5.81304795846567</v>
+        <v>5.793179848367624</v>
       </c>
       <c r="P8" t="n">
-        <v>333.411879246503</v>
+        <v>333.4277815860233</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25513,28 +25687,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2744959388931765</v>
+        <v>0.2784719617921169</v>
       </c>
       <c r="J9" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K9" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09022472680213034</v>
+        <v>0.09371075334804757</v>
       </c>
       <c r="M9" t="n">
-        <v>4.890460147962036</v>
+        <v>4.879841698070003</v>
       </c>
       <c r="N9" t="n">
-        <v>46.39097278864994</v>
+        <v>46.12436728652954</v>
       </c>
       <c r="O9" t="n">
-        <v>6.811091894010089</v>
+        <v>6.791492272433912</v>
       </c>
       <c r="P9" t="n">
-        <v>329.524385426123</v>
+        <v>329.4833529537527</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25591,28 +25765,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2996822495950387</v>
+        <v>0.3083185477241141</v>
       </c>
       <c r="J10" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K10" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1003061345496086</v>
+        <v>0.1063083682343009</v>
       </c>
       <c r="M10" t="n">
-        <v>5.147632638388164</v>
+        <v>5.165886158135517</v>
       </c>
       <c r="N10" t="n">
-        <v>49.18609951312595</v>
+        <v>49.14842644351477</v>
       </c>
       <c r="O10" t="n">
-        <v>7.013280224910876</v>
+        <v>7.010593872384476</v>
       </c>
       <c r="P10" t="n">
-        <v>333.1002726013564</v>
+        <v>333.011148298526</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25669,28 +25843,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1663527887080425</v>
+        <v>0.1751840292008406</v>
       </c>
       <c r="J11" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K11" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03965018287025868</v>
+        <v>0.04404921591017685</v>
       </c>
       <c r="M11" t="n">
-        <v>4.90589025846147</v>
+        <v>4.924594089833785</v>
       </c>
       <c r="N11" t="n">
-        <v>40.92583169423311</v>
+        <v>40.9615562463987</v>
       </c>
       <c r="O11" t="n">
-        <v>6.397330044185082</v>
+        <v>6.400121580595068</v>
       </c>
       <c r="P11" t="n">
-        <v>330.0481563802659</v>
+        <v>329.9570185217915</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25747,28 +25921,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04083279739457066</v>
+        <v>-0.02413592112379158</v>
       </c>
       <c r="J12" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K12" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001619141842067573</v>
+        <v>0.0005638838853180284</v>
       </c>
       <c r="M12" t="n">
-        <v>6.081962931200586</v>
+        <v>6.157407365391261</v>
       </c>
       <c r="N12" t="n">
-        <v>62.77441822618198</v>
+        <v>63.50138341996119</v>
       </c>
       <c r="O12" t="n">
-        <v>7.923030873736513</v>
+        <v>7.9687755282704</v>
       </c>
       <c r="P12" t="n">
-        <v>331.962083094972</v>
+        <v>331.7897731852424</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25825,28 +25999,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08104601734115496</v>
+        <v>-0.06533657309789002</v>
       </c>
       <c r="J13" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004223450981322485</v>
+        <v>0.002758163371423539</v>
       </c>
       <c r="M13" t="n">
-        <v>7.71300468287697</v>
+        <v>7.747827688660205</v>
       </c>
       <c r="N13" t="n">
-        <v>94.56074207684445</v>
+        <v>94.92558502910971</v>
       </c>
       <c r="O13" t="n">
-        <v>9.724234781042899</v>
+        <v>9.742976189497217</v>
       </c>
       <c r="P13" t="n">
-        <v>330.8739823849118</v>
+        <v>330.7118658311486</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25884,7 +26058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N415"/>
+  <dimension ref="A1:N418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55767,6 +55941,222 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-41.18988321443394,175.99234675476123</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-41.19051942972863,175.9920295755634</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-41.19116827792639,175.99177686772407</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-41.191826576144656,175.99152760240867</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-41.19250303405017,175.99135854774093</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-41.19319151872843,175.9912889259311</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-41.19387689042383,175.99130569493408</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-41.194554403658834,175.99133862640684</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-41.19523060316842,175.99143506463147</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-41.19591028051393,175.99151506939987</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-41.19656832755322,175.9917253102499</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-41.197234752185636,175.99188449300658</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-41.18988466151587,175.99235413611413</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-41.19051981411333,175.99203153625336</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-41.19116843620343,175.99177767507473</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-41.19182561964579,175.9915217806249</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-41.1925021172494,175.99135041583153</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-41.19319062053193,175.9912713303167</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-41.19387693329377,175.99129449387823</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-41.19455450051254,175.99133302721728</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-41.195231361883344,175.99142642383578</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-41.19590910979728,175.99152217132533</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-41.19656863318295,175.9917235691518</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-41.197234752185636,175.99188449300658</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-41.18988452585195,175.99235344411227</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-41.19052006283282,175.99203280493512</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-41.1911693406435,175.99178228850727</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-41.19182699700408,175.99153016399356</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-41.192502648728166,175.99135512998188</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-41.19319049915383,175.99126895253102</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-41.19387695472834,175.99128889335026</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-41.194554416023145,175.9913379116167</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-41.195231361883344,175.99142642383578</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-41.19590951283093,175.99151972640018</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-41.19656842942979,175.99172472988386</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-41.197236979592304,175.9918722102732</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N418"/>
+  <dimension ref="A1:N422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20514,6 +20514,198 @@
         <v>340.16</v>
       </c>
       <c r="N418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>334.24</v>
+      </c>
+      <c r="C419" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D419" t="n">
+        <v>327.34</v>
+      </c>
+      <c r="E419" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="F419" t="n">
+        <v>327.51</v>
+      </c>
+      <c r="G419" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="H419" t="n">
+        <v>335.98</v>
+      </c>
+      <c r="I419" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="J419" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="K419" t="n">
+        <v>340.79</v>
+      </c>
+      <c r="L419" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="M419" t="n">
+        <v>339.87</v>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>333.92</v>
+      </c>
+      <c r="C420" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="D420" t="n">
+        <v>328.14</v>
+      </c>
+      <c r="E420" t="n">
+        <v>327.86</v>
+      </c>
+      <c r="F420" t="n">
+        <v>328.36</v>
+      </c>
+      <c r="G420" t="n">
+        <v>331.95</v>
+      </c>
+      <c r="H420" t="n">
+        <v>335.62</v>
+      </c>
+      <c r="I420" t="n">
+        <v>339.29</v>
+      </c>
+      <c r="J420" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="K420" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="L420" t="n">
+        <v>341.96</v>
+      </c>
+      <c r="M420" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>334.21</v>
+      </c>
+      <c r="C421" t="n">
+        <v>328.29</v>
+      </c>
+      <c r="D421" t="n">
+        <v>328.56</v>
+      </c>
+      <c r="E421" t="n">
+        <v>328.67</v>
+      </c>
+      <c r="F421" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="G421" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="H421" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="I421" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="J421" t="n">
+        <v>344.95</v>
+      </c>
+      <c r="K421" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="L421" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="M421" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>334.97</v>
+      </c>
+      <c r="C422" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="D422" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="E422" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="F422" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="G422" t="n">
+        <v>333.53</v>
+      </c>
+      <c r="H422" t="n">
+        <v>335.98</v>
+      </c>
+      <c r="I422" t="n">
+        <v>338.07</v>
+      </c>
+      <c r="J422" t="n">
+        <v>343.85</v>
+      </c>
+      <c r="K422" t="n">
+        <v>337.73</v>
+      </c>
+      <c r="L422" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="M422" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="N422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20530,7 +20722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24973,6 +25165,56 @@
       </c>
       <c r="B444" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-07 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>
@@ -25141,28 +25383,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.197579956306436</v>
+        <v>-0.2063950941260583</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09783016782591047</v>
+        <v>0.1064920011896784</v>
       </c>
       <c r="M2" t="n">
-        <v>3.679019194783713</v>
+        <v>3.692536872398565</v>
       </c>
       <c r="N2" t="n">
-        <v>22.14069999612402</v>
+        <v>22.18623876353959</v>
       </c>
       <c r="O2" t="n">
-        <v>4.705390525357489</v>
+        <v>4.710227039489666</v>
       </c>
       <c r="P2" t="n">
-        <v>344.9140113167222</v>
+        <v>345.0051854829078</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25219,28 +25461,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1720157771998533</v>
+        <v>-0.180402433039881</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06992266892267185</v>
+        <v>0.07701918270191033</v>
       </c>
       <c r="M3" t="n">
-        <v>3.638642179764911</v>
+        <v>3.641388955715785</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2062604491517</v>
+        <v>24.20928905531626</v>
       </c>
       <c r="O3" t="n">
-        <v>4.919985817982782</v>
+        <v>4.92029359442262</v>
       </c>
       <c r="P3" t="n">
-        <v>337.8471715356072</v>
+        <v>337.9339091219202</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25297,28 +25539,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08678211721625002</v>
+        <v>-0.09172508185790811</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01681746742680745</v>
+        <v>0.01903891919023393</v>
       </c>
       <c r="M4" t="n">
-        <v>3.745135255459675</v>
+        <v>3.728284818294571</v>
       </c>
       <c r="N4" t="n">
-        <v>27.07846968544984</v>
+        <v>26.90848138404501</v>
       </c>
       <c r="O4" t="n">
-        <v>5.203697693510821</v>
+        <v>5.187338564624929</v>
       </c>
       <c r="P4" t="n">
-        <v>333.7331990660118</v>
+        <v>333.7843058771365</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25375,28 +25617,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09721413968403131</v>
+        <v>-0.1040950633599878</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02029119987915562</v>
+        <v>0.02348980902173148</v>
       </c>
       <c r="M5" t="n">
-        <v>4.013901653864631</v>
+        <v>4.007822293104379</v>
       </c>
       <c r="N5" t="n">
-        <v>28.06326709130397</v>
+        <v>27.96153747551472</v>
       </c>
       <c r="O5" t="n">
-        <v>5.297477427163232</v>
+        <v>5.287867006224222</v>
       </c>
       <c r="P5" t="n">
-        <v>335.0694626589004</v>
+        <v>335.1406127137242</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25453,28 +25695,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01859988883813053</v>
+        <v>0.009154732149003674</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009060729434116066</v>
+        <v>0.0002209795826481065</v>
       </c>
       <c r="M6" t="n">
-        <v>3.833872705817264</v>
+        <v>3.848150929349584</v>
       </c>
       <c r="N6" t="n">
-        <v>23.46140031130336</v>
+        <v>23.53675789875674</v>
       </c>
       <c r="O6" t="n">
-        <v>4.843696967328092</v>
+        <v>4.85146966379846</v>
       </c>
       <c r="P6" t="n">
-        <v>333.7435195337139</v>
+        <v>333.8412000653364</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25531,28 +25773,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07934334707671638</v>
+        <v>0.06926633833142418</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01498966897117504</v>
+        <v>0.01152683635018847</v>
       </c>
       <c r="M7" t="n">
-        <v>3.80003960596512</v>
+        <v>3.818160559940682</v>
       </c>
       <c r="N7" t="n">
-        <v>25.44250408263069</v>
+        <v>25.53893019495498</v>
       </c>
       <c r="O7" t="n">
-        <v>5.044056312396868</v>
+        <v>5.053605662787213</v>
       </c>
       <c r="P7" t="n">
-        <v>336.25098414442</v>
+        <v>336.3552006352722</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25609,28 +25851,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.161400481751841</v>
+        <v>0.1581472019666127</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K8" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04556306622612993</v>
+        <v>0.0445739005183895</v>
       </c>
       <c r="M8" t="n">
-        <v>4.201227081358475</v>
+        <v>4.172432322240155</v>
       </c>
       <c r="N8" t="n">
-        <v>33.56093275553273</v>
+        <v>33.27690846346751</v>
       </c>
       <c r="O8" t="n">
-        <v>5.793179848367624</v>
+        <v>5.768614085156634</v>
       </c>
       <c r="P8" t="n">
-        <v>333.4277815860233</v>
+        <v>333.461432327455</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25687,28 +25929,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2784719617921169</v>
+        <v>0.2819695862035795</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K9" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09371075334804757</v>
+        <v>0.09740572268245096</v>
       </c>
       <c r="M9" t="n">
-        <v>4.879841698070003</v>
+        <v>4.854956040829609</v>
       </c>
       <c r="N9" t="n">
-        <v>46.12436728652954</v>
+        <v>45.73157117606393</v>
       </c>
       <c r="O9" t="n">
-        <v>6.791492272433912</v>
+        <v>6.762512194152698</v>
       </c>
       <c r="P9" t="n">
-        <v>329.4833529537527</v>
+        <v>329.4471926244447</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25765,28 +26007,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3083185477241141</v>
+        <v>0.3154463202289075</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1063083682343009</v>
+        <v>0.1122152284180611</v>
       </c>
       <c r="M10" t="n">
-        <v>5.165886158135517</v>
+        <v>5.162805130977116</v>
       </c>
       <c r="N10" t="n">
-        <v>49.14842644351477</v>
+        <v>48.86639602191064</v>
       </c>
       <c r="O10" t="n">
-        <v>7.010593872384476</v>
+        <v>6.990450344713897</v>
       </c>
       <c r="P10" t="n">
-        <v>333.011148298526</v>
+        <v>332.9374523465012</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25843,28 +26085,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1751840292008406</v>
+        <v>0.1825899208475135</v>
       </c>
       <c r="J11" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K11" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04404921591017685</v>
+        <v>0.04831312673071286</v>
       </c>
       <c r="M11" t="n">
-        <v>4.924594089833785</v>
+        <v>4.922951358459953</v>
       </c>
       <c r="N11" t="n">
-        <v>40.9615562463987</v>
+        <v>40.76486612540104</v>
       </c>
       <c r="O11" t="n">
-        <v>6.400121580595068</v>
+        <v>6.384736966030867</v>
       </c>
       <c r="P11" t="n">
-        <v>329.9570185217915</v>
+        <v>329.8804390083329</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25921,28 +26163,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02413592112379158</v>
+        <v>-0.006431712199800905</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K12" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005638838853180284</v>
+        <v>4.016222635894184e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>6.157407365391261</v>
+        <v>6.225110907548296</v>
       </c>
       <c r="N12" t="n">
-        <v>63.50138341996119</v>
+        <v>63.93246788157841</v>
       </c>
       <c r="O12" t="n">
-        <v>7.9687755282704</v>
+        <v>7.995778128586261</v>
       </c>
       <c r="P12" t="n">
-        <v>331.7897731852424</v>
+        <v>331.6066620396671</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25999,28 +26241,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06533657309789002</v>
+        <v>-0.04890760874856873</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K13" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002758163371423539</v>
+        <v>0.001561862612854847</v>
       </c>
       <c r="M13" t="n">
-        <v>7.747827688660205</v>
+        <v>7.768773592523831</v>
       </c>
       <c r="N13" t="n">
-        <v>94.92558502910971</v>
+        <v>94.91496164741164</v>
       </c>
       <c r="O13" t="n">
-        <v>9.742976189497217</v>
+        <v>9.742430992694361</v>
       </c>
       <c r="P13" t="n">
-        <v>330.7118658311486</v>
+        <v>330.5419471686171</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26058,7 +26300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N418"/>
+  <dimension ref="A1:N422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56157,6 +56399,294 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-41.18988452585195,175.99235344411227</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-41.19052006283282,175.99203280493512</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-41.1911693406435,175.99178228850727</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-41.19182699700408,175.99153016399356</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-41.192502648728166,175.99135512998188</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-41.19319049915383,175.99126895253102</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-41.19387695472834,175.99128889335026</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-41.194554416023145,175.9913379116167</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-41.195231361883344,175.99142642383578</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-41.195910741123626,175.9915122751996</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-41.19656999832875,175.99171579224662</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-41.197237588976925,175.99186884990254</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-41.18988380231104,175.9923497534358</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-41.1905201306654,175.99203315093925</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-41.1911711495231,175.99179151537265</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-41.191828508271485,175.9915393624123</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-41.19250377811993,175.99136514755156</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-41.19319077832341,175.9912744214381</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-41.19387697114611,175.99128460358415</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-41.194554585001725,175.99132814281785</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-41.19523317032458,175.9914058279655</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-41.19591331285995,175.9914966742474</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-41.196572219236465,175.99170314026588</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-41.19723903889167,175.99186085453772</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-41.18988445801999,175.99235309811135</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-41.19052128381917,175.99203903300932</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-41.19117209918458,175.99179635947718</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-41.191830057798036,175.99154879370286</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-41.19250452218931,175.99137174736234</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-41.193191172801725,175.99128214924173</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-41.193876962937246,175.9912867484672</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-41.19455467567281,175.99132290102332</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-41.19523413690372,175.9913948198274</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-41.195915308833,175.99148456604476</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-41.19657399188661,175.99169304189525</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-41.19724071995156,175.99185158454898</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-41.189886176429226,175.99236186346826</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-41.190522979632995,175.99204768311273</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-41.19117478989098,175.9918100844407</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-41.19183221948191,175.99156195093596</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-41.19250555857103,175.99138093995614</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-41.19319173720826,175.99129320594542</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-41.19387695472834,175.99128889335026</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-41.19455483640735,175.99131360875108</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-41.19523528016804,175.9913817994485</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-41.19591661389161,175.99147664914258</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-41.196574949524816,175.99168758645342</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-41.197242569116604,175.9918413875608</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20708,6 +20708,198 @@
       <c r="N422" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>334.56</v>
+      </c>
+      <c r="C423" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="D423" t="n">
+        <v>330</v>
+      </c>
+      <c r="E423" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="F423" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="G423" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="H423" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="I423" t="n">
+        <v>336.55</v>
+      </c>
+      <c r="J423" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="K423" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="L423" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="M423" t="n">
+        <v>335.71</v>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:47+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="C424" t="n">
+        <v>329.31</v>
+      </c>
+      <c r="D424" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="E424" t="n">
+        <v>329.84</v>
+      </c>
+      <c r="F424" t="n">
+        <v>330.04</v>
+      </c>
+      <c r="G424" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="H424" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="I424" t="n">
+        <v>335.27</v>
+      </c>
+      <c r="J424" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="K424" t="n">
+        <v>335.54</v>
+      </c>
+      <c r="L424" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="M424" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>335.14</v>
+      </c>
+      <c r="C425" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="D425" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="E425" t="n">
+        <v>330.74</v>
+      </c>
+      <c r="F425" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="G425" t="n">
+        <v>333.55</v>
+      </c>
+      <c r="H425" t="n">
+        <v>334.12</v>
+      </c>
+      <c r="I425" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="J425" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="K425" t="n">
+        <v>334.91</v>
+      </c>
+      <c r="L425" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="M425" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>336.01</v>
+      </c>
+      <c r="C426" t="n">
+        <v>330.54</v>
+      </c>
+      <c r="D426" t="n">
+        <v>331</v>
+      </c>
+      <c r="E426" t="n">
+        <v>331.73</v>
+      </c>
+      <c r="F426" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="G426" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="H426" t="n">
+        <v>334.02</v>
+      </c>
+      <c r="I426" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="J426" t="n">
+        <v>338.51</v>
+      </c>
+      <c r="K426" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="L426" t="n">
+        <v>335.75</v>
+      </c>
+      <c r="M426" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25215,6 +25407,56 @@
       </c>
       <c r="B449" t="n">
         <v>-0.02</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -25383,28 +25625,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2063950941260583</v>
+        <v>-0.2134327340593585</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1064920011896784</v>
+        <v>0.1141205219821255</v>
       </c>
       <c r="M2" t="n">
-        <v>3.692536872398565</v>
+        <v>3.697047745293889</v>
       </c>
       <c r="N2" t="n">
-        <v>22.18623876353959</v>
+        <v>22.14730150871874</v>
       </c>
       <c r="O2" t="n">
-        <v>4.710227039489666</v>
+        <v>4.706091957103977</v>
       </c>
       <c r="P2" t="n">
-        <v>345.0051854829078</v>
+        <v>345.0783071635088</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25461,28 +25703,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.180402433039881</v>
+        <v>-0.1858581911807058</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07701918270191033</v>
+        <v>0.08242470664855583</v>
       </c>
       <c r="M3" t="n">
-        <v>3.641388955715785</v>
+        <v>3.631619751064535</v>
       </c>
       <c r="N3" t="n">
-        <v>24.20928905531626</v>
+        <v>24.08438630131326</v>
       </c>
       <c r="O3" t="n">
-        <v>4.92029359442262</v>
+        <v>4.907584568941554</v>
       </c>
       <c r="P3" t="n">
-        <v>337.9339091219202</v>
+        <v>337.990593310528</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25539,28 +25781,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09172508185790811</v>
+        <v>-0.09334715396785802</v>
       </c>
       <c r="J4" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01903891919023393</v>
+        <v>0.02005540263034755</v>
       </c>
       <c r="M4" t="n">
-        <v>3.728284818294571</v>
+        <v>3.699263468874701</v>
       </c>
       <c r="N4" t="n">
-        <v>26.90848138404501</v>
+        <v>26.66614102192766</v>
       </c>
       <c r="O4" t="n">
-        <v>5.187338564624929</v>
+        <v>5.163926899359407</v>
       </c>
       <c r="P4" t="n">
-        <v>333.7843058771365</v>
+        <v>333.801154337413</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25617,28 +25859,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1040950633599878</v>
+        <v>-0.1070446766877964</v>
       </c>
       <c r="J5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02348980902173148</v>
+        <v>0.02522410743236037</v>
       </c>
       <c r="M5" t="n">
-        <v>4.007822293104379</v>
+        <v>3.983763097161003</v>
       </c>
       <c r="N5" t="n">
-        <v>27.96153747551472</v>
+        <v>27.73364761882717</v>
       </c>
       <c r="O5" t="n">
-        <v>5.287867006224222</v>
+        <v>5.266274548371664</v>
       </c>
       <c r="P5" t="n">
-        <v>335.1406127137242</v>
+        <v>335.1712508615247</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25695,28 +25937,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009154732149003674</v>
+        <v>0.002967807607267569</v>
       </c>
       <c r="J6" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002209795826481065</v>
+        <v>2.352518828951933e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.848150929349584</v>
+        <v>3.844872829059056</v>
       </c>
       <c r="N6" t="n">
-        <v>23.53675789875674</v>
+        <v>23.44855222392023</v>
       </c>
       <c r="O6" t="n">
-        <v>4.85146966379846</v>
+        <v>4.842370517000969</v>
       </c>
       <c r="P6" t="n">
-        <v>333.8412000653364</v>
+        <v>333.9054800858814</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25773,28 +26015,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06926633833142418</v>
+        <v>0.06112147677981732</v>
       </c>
       <c r="J7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01152683635018847</v>
+        <v>0.009083739524747947</v>
       </c>
       <c r="M7" t="n">
-        <v>3.818160559940682</v>
+        <v>3.826548271157846</v>
       </c>
       <c r="N7" t="n">
-        <v>25.53893019495498</v>
+        <v>25.52394683882564</v>
       </c>
       <c r="O7" t="n">
-        <v>5.053605662787213</v>
+        <v>5.052123003136963</v>
       </c>
       <c r="P7" t="n">
-        <v>336.3552006352722</v>
+        <v>336.439829909846</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25851,28 +26093,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1581472019666127</v>
+        <v>0.1524741468081068</v>
       </c>
       <c r="J8" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K8" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0445739005183895</v>
+        <v>0.04216913647308507</v>
       </c>
       <c r="M8" t="n">
-        <v>4.172432322240155</v>
+        <v>4.152157922647285</v>
       </c>
       <c r="N8" t="n">
-        <v>33.27690846346751</v>
+        <v>33.07306267967457</v>
       </c>
       <c r="O8" t="n">
-        <v>5.768614085156634</v>
+        <v>5.750918420537243</v>
       </c>
       <c r="P8" t="n">
-        <v>333.461432327455</v>
+        <v>333.5203858282384</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25929,28 +26171,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2819695862035795</v>
+        <v>0.2786775201930529</v>
       </c>
       <c r="J9" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K9" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09740572268245096</v>
+        <v>0.09687234894748842</v>
       </c>
       <c r="M9" t="n">
-        <v>4.854956040829609</v>
+        <v>4.825987113706356</v>
       </c>
       <c r="N9" t="n">
-        <v>45.73157117606393</v>
+        <v>45.34621620646114</v>
       </c>
       <c r="O9" t="n">
-        <v>6.762512194152698</v>
+        <v>6.733959920170386</v>
       </c>
       <c r="P9" t="n">
-        <v>329.4471926244447</v>
+        <v>329.481413405454</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26007,28 +26249,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3154463202289075</v>
+        <v>0.3133561929278684</v>
       </c>
       <c r="J10" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K10" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1122152284180611</v>
+        <v>0.1126562556353043</v>
       </c>
       <c r="M10" t="n">
-        <v>5.162805130977116</v>
+        <v>5.127964849885795</v>
       </c>
       <c r="N10" t="n">
-        <v>48.86639602191064</v>
+        <v>48.43965205042976</v>
       </c>
       <c r="O10" t="n">
-        <v>6.990450344713897</v>
+        <v>6.959860059687246</v>
       </c>
       <c r="P10" t="n">
-        <v>332.9374523465012</v>
+        <v>332.9591907034993</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26085,28 +26327,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1825899208475135</v>
+        <v>0.1831803793181913</v>
       </c>
       <c r="J11" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K11" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04831312673071286</v>
+        <v>0.04945420228975594</v>
       </c>
       <c r="M11" t="n">
-        <v>4.922951358459953</v>
+        <v>4.885929874172317</v>
       </c>
       <c r="N11" t="n">
-        <v>40.76486612540104</v>
+        <v>40.39388495742978</v>
       </c>
       <c r="O11" t="n">
-        <v>6.384736966030867</v>
+        <v>6.355618377265094</v>
       </c>
       <c r="P11" t="n">
-        <v>329.8804390083329</v>
+        <v>329.8743192964948</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26163,28 +26405,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.006431712199800905</v>
+        <v>0.003913609924075911</v>
       </c>
       <c r="J12" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K12" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L12" t="n">
-        <v>4.016222635894184e-05</v>
+        <v>1.505645917465603e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>6.225110907548296</v>
+        <v>6.239845665305745</v>
       </c>
       <c r="N12" t="n">
-        <v>63.93246788157841</v>
+        <v>63.71087276114167</v>
       </c>
       <c r="O12" t="n">
-        <v>7.995778128586261</v>
+        <v>7.981909092512998</v>
       </c>
       <c r="P12" t="n">
-        <v>331.6066620396671</v>
+        <v>331.4991824129154</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26241,28 +26483,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04890760874856873</v>
+        <v>-0.04040566150789242</v>
       </c>
       <c r="J13" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K13" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001561862612854847</v>
+        <v>0.001083441493989756</v>
       </c>
       <c r="M13" t="n">
-        <v>7.768773592523831</v>
+        <v>7.744824033479689</v>
       </c>
       <c r="N13" t="n">
-        <v>94.91496164741164</v>
+        <v>94.27489590416204</v>
       </c>
       <c r="O13" t="n">
-        <v>9.742430992694361</v>
+        <v>9.709526039110356</v>
       </c>
       <c r="P13" t="n">
-        <v>330.5419471686171</v>
+        <v>330.453615547809</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26300,7 +26542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N422"/>
+  <dimension ref="A1:N426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56687,6 +56929,294 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-41.18988524939276,175.99235713478882</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-41.19052349968244,175.9920503358112</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-41.19117535516522,175.99181296783655</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-41.19183223861186,175.99156206737166</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-41.19250523968443,175.9913781114657</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-41.19319123349066,175.9912833381346</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-41.19387700945364,175.99127459412983</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-41.19455514963144,175.9912955007332</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-41.19523694309536,175.9913628607146</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-41.195918648246625,175.9914643080885</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-41.19657723155531,175.99167458625087</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-41.19724633048366,175.99182064595792</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:47+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-41.18988597293343,175.99236082546543</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-41.190523590125814,175.99205079715006</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-41.19117490294583,175.99181066111987</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-41.19183229600168,175.99156241667876</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-41.19250601032692,175.99138494698428</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-41.193191482315115,175.99128821259538</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-41.19387703225531,175.99126863612128</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-41.1945554133969,175.99128025187574</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-41.19523862680612,175.99134368524534</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-41.195920816944415,175.99145115205826</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-41.19657926908131,175.99166297892629</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-41.197247927487545,175.99181183946652</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-41.18988656081016,175.99236382414023</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-41.1905247658895,175.99205679455545</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-41.19117641788059,175.9918183886208</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-41.191834017695655,175.99157289589155</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-41.19250672782131,175.9913913110879</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-41.193191749346006,175.991293443724</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-41.193877039551786,175.99126672955853</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-41.19455559885579,175.9912695300227</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-41.19523985321072,175.9913297179275</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-41.195922026040755,175.99144381727987</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-41.196582080865305,175.99164696081715</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-41.1972507012296,175.99179654398037</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-41.1898885279355,175.99237385816784</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-41.19052637125864,175.9920649833208</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-41.19117761626144,175.9918245014203</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-41.191835911557924,175.9915844230262</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-41.19250763133222,175.9913993251445</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-41.193191888930265,175.99129617817766</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-41.19387704411207,175.99126553795682</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-41.19455564625066,175.99126678999357</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-41.19524083017591,175.99131859141963</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-41.195924501808044,175.9914287984471</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-41.1965848722719,175.99163105877975</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-41.197251520743905,175.99179202485917</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
